--- a/docs/03_test/部署登録ブラックボックステスト.xlsx
+++ b/docs/03_test/部署登録ブラックボックステスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13776F7A-26CD-4814-B0BF-77A042584336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27737F48-E5EC-4C4D-AD84-2E5779DB934D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ディシジョンテーブル" sheetId="1" r:id="rId1"/>
@@ -44,145 +44,146 @@
     <t>C3: 部署名が非nullか</t>
   </si>
   <si>
+    <t>C5: 部署名が日本語かつ最後が「部」か</t>
+  </si>
+  <si>
+    <t>C6: 同一の部署番号が存在しないか</t>
+  </si>
+  <si>
+    <t>C7: 同一の部署名が存在しないか</t>
+  </si>
+  <si>
+    <t>A1: エラー「部署番号は必須です」</t>
+  </si>
+  <si>
+    <t>A2: エラー「100～999までの値で入力してください」</t>
+  </si>
+  <si>
+    <t>A3: エラー「部署名は入力必須です」</t>
+  </si>
+  <si>
+    <t>A4: エラー「20文字以内で入力してください」</t>
+  </si>
+  <si>
+    <t>A5: エラー「適切な形式(例:総務部)で入力...」</t>
+  </si>
+  <si>
+    <t>A6: エラー「その部署番号は既に使用されています」</t>
+  </si>
+  <si>
+    <t>A7: エラー「その部署名は既に使用されています」</t>
+  </si>
+  <si>
+    <t>A8: 登録を続行（成功）</t>
+  </si>
+  <si>
+    <t>テストID</t>
+  </si>
+  <si>
+    <t>対象ルール</t>
+  </si>
+  <si>
+    <t>部署番号</t>
+  </si>
+  <si>
+    <t>部署名</t>
+  </si>
+  <si>
+    <t>期待結果</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>null (未入力)</t>
+  </si>
+  <si>
+    <t>総務部</t>
+  </si>
+  <si>
+    <t>「部署番号は必須です」</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>「100～999までの値で入力してください」</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>「部署名は入力必須です」</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>あ...(20文字) + 部</t>
+  </si>
+  <si>
+    <t>「20文字以内で入力してください」</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>営業課</t>
+  </si>
+  <si>
+    <t>「適切な形式(例:総務部)で入力してください」</t>
+  </si>
+  <si>
+    <t>IT部</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>開発部</t>
+  </si>
+  <si>
+    <t>「その部署番号は既に使用されています」</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>人事部</t>
+  </si>
+  <si>
+    <t>「その部署名は既に使用されています」</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>部</t>
+  </si>
+  <si>
+    <t>登録成功</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あ...(19文字) + 部 </t>
+  </si>
+  <si>
+    <t>企画部</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>C1: 部署番号が非nullか</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>C4: 部署名が20文字以内か</t>
-  </si>
-  <si>
-    <t>C5: 部署名が日本語かつ最後が「部」か</t>
-  </si>
-  <si>
-    <t>C6: 同一の部署番号が存在しないか</t>
-  </si>
-  <si>
-    <t>C7: 同一の部署名が存在しないか</t>
-  </si>
-  <si>
-    <t>A1: エラー「部署番号は必須です」</t>
-  </si>
-  <si>
-    <t>A2: エラー「100～999までの値で入力してください」</t>
-  </si>
-  <si>
-    <t>A3: エラー「部署名は入力必須です」</t>
-  </si>
-  <si>
-    <t>A4: エラー「20文字以内で入力してください」</t>
-  </si>
-  <si>
-    <t>A5: エラー「適切な形式(例:総務部)で入力...」</t>
-  </si>
-  <si>
-    <t>A6: エラー「その部署番号は既に使用されています」</t>
-  </si>
-  <si>
-    <t>A7: エラー「その部署名は既に使用されています」</t>
-  </si>
-  <si>
-    <t>A8: 登録を続行（成功）</t>
-  </si>
-  <si>
-    <t>テストID</t>
-  </si>
-  <si>
-    <t>対象ルール</t>
-  </si>
-  <si>
-    <t>部署番号</t>
-  </si>
-  <si>
-    <t>部署名</t>
-  </si>
-  <si>
-    <t>期待結果</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>null (未入力)</t>
-  </si>
-  <si>
-    <t>総務部</t>
-  </si>
-  <si>
-    <t>「部署番号は必須です」</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>「100～999までの値で入力してください」</t>
-  </si>
-  <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>「部署名は入力必須です」</t>
-  </si>
-  <si>
-    <t>""</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>あ...(20文字) + 部</t>
-  </si>
-  <si>
-    <t>「20文字以内で入力してください」</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>営業課</t>
-  </si>
-  <si>
-    <t>「適切な形式(例:総務部)で入力してください」</t>
-  </si>
-  <si>
-    <t>IT部</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>開発部</t>
-  </si>
-  <si>
-    <t>「その部署番号は既に使用されています」</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>人事部</t>
-  </si>
-  <si>
-    <t>「その部署名は既に使用されています」</t>
-  </si>
-  <si>
-    <t>R8</t>
-  </si>
-  <si>
-    <t>部</t>
-  </si>
-  <si>
-    <t>登録成功</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あ...(19文字) + 部 </t>
-  </si>
-  <si>
-    <t>企画部</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>C1: 部署番号が非nullか</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -274,24 +275,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -520,46 +521,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="10">
+      <c r="A2" s="9"/>
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="4">
         <v>2</v>
       </c>
-      <c r="D2" s="10">
-        <v>3</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="4">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4">
         <v>4</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="4">
         <v>5</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="4">
         <v>6</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="4">
         <v>7</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="4">
         <v>8</v>
       </c>
       <c r="Q2" s="1"/>
@@ -567,30 +568,30 @@
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="C3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q3" s="1"/>
@@ -600,28 +601,28 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="8" t="s">
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q4" s="1"/>
@@ -631,28 +632,28 @@
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="8" t="s">
+      <c r="E5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q5" s="1"/>
@@ -660,30 +661,30 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="8" t="s">
+      <c r="F6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q6" s="1"/>
@@ -691,30 +692,30 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="G7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q7" s="1"/>
@@ -722,30 +723,30 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="H8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q8" s="1"/>
@@ -753,30 +754,30 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="6" t="s">
         <v>3</v>
       </c>
       <c r="Q9" s="1"/>
@@ -784,148 +785,148 @@
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+        <v>11</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+        <v>14</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
+        <v>15</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I16" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="6"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1934,297 +1935,297 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
-        <v>2</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="7">
+        <v>99</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="11">
-        <v>99</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="7">
+        <v>100.5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="11">
-        <v>1000</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
-        <v>4</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="11">
-        <v>100.5</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>6</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="C7" s="7">
+        <v>300</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="11">
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="7">
         <v>300</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
-        <v>7</v>
-      </c>
-      <c r="B8" s="10" t="s">
+      <c r="E8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="11">
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="7">
         <v>300</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>8</v>
-      </c>
-      <c r="B9" s="10" t="s">
+      <c r="D9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="11">
+      <c r="E9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="7">
         <v>300</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="11">
+      <c r="C11" s="7">
         <v>300</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>10</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="11">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="7">
+        <v>200</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="7">
         <v>300</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
-        <v>11</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="11">
-        <v>200</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>12</v>
-      </c>
-      <c r="B13" s="10" t="s">
+      <c r="D13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="11">
-        <v>300</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
-        <v>13</v>
-      </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="7">
+        <v>100</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="11">
-        <v>100</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="7">
+        <v>999</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>14</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="11">
-        <v>999</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="7">
+        <v>500</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
-        <v>15</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="11">
-        <v>500</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/docs/03_test/部署登録ブラックボックステスト.xlsx
+++ b/docs/03_test/部署登録ブラックボックステスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27737F48-E5EC-4C4D-AD84-2E5779DB934D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEFAD54-B76F-4C13-BBD1-D93514C0F69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ディシジョンテーブル" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="54">
   <si>
     <t>条件 / アクション</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>A8: 登録を続行（成功）</t>
-  </si>
-  <si>
-    <t>テストID</t>
   </si>
   <si>
     <t>対象ルール</t>
@@ -184,6 +181,10 @@
   </si>
   <si>
     <t>C4: 部署名が20文字以内か</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>テストNo</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -568,7 +569,7 @@
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>2</v>
@@ -661,7 +662,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>5</v>
@@ -1936,19 +1937,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F1" s="2"/>
     </row>
@@ -1957,16 +1958,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="F2" s="1"/>
     </row>
@@ -1975,16 +1976,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="7">
         <v>99</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1"/>
     </row>
@@ -1993,16 +1994,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="7">
         <v>1000</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1"/>
     </row>
@@ -2011,16 +2012,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="C5" s="7">
-        <v>100.5</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -2029,16 +2030,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="7" t="s">
         <v>29</v>
       </c>
+      <c r="C6" s="7">
+        <v>300</v>
+      </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1"/>
     </row>
@@ -2047,16 +2048,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="7">
         <v>300</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1"/>
     </row>
@@ -2065,16 +2066,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="7">
         <v>300</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F8" s="1"/>
     </row>
@@ -2083,16 +2084,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" s="7">
         <v>300</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F9" s="1"/>
     </row>
@@ -2101,16 +2102,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="7">
         <v>300</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F10" s="1"/>
     </row>
@@ -2119,16 +2120,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C11" s="7">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1"/>
     </row>
@@ -2137,16 +2138,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C12" s="7">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F12" s="1"/>
     </row>
@@ -2155,16 +2156,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C13" s="7">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -2173,16 +2174,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="7">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="F14" s="1"/>
     </row>
@@ -2191,41 +2192,26 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="7">
-        <v>999</v>
+        <v>500</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="7">
-        <v>500</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
